--- a/data/raw/CPI.xlsx
+++ b/data/raw/CPI.xlsx
@@ -1,21 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1249f38fb8963dce/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1249f38fb8963dce/Desktop/Agri/inflation-forecasting-india/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E4442FA-9502-414F-B731-B1BA97F2B3AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{5E4442FA-9502-414F-B731-B1BA97F2B3AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04BB771F-B3C0-445A-AB12-359160E2EBE3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D547D527-36DC-4F83-B124-7FC9947A7CAE}"/>
   </bookViews>
   <sheets>
     <sheet name="Report_3_18_2026_8_47_08" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -659,10 +670,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -724,6 +735,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1036,15 +1051,15 @@
   <sheetData>
     <row r="1" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
       <c r="I1" s="12"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
